--- a/docs/Logic Requirements/Ageipelago William Wallace.xlsx
+++ b/docs/Logic Requirements/Ageipelago William Wallace.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B02CA9-6883-4A3E-8AF4-B75F246DDA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B3BA43-3F6A-4476-A7F7-5769A803E51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" activeTab="7" xr2:uid="{1D996FA3-8E71-4AAB-A721-F834CDA60D66}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="132">
   <si>
     <t>Scenario</t>
   </si>
@@ -675,9 +675,6 @@
     <t>Watch Tower</t>
   </si>
   <si>
-    <t>Galleon</t>
-  </si>
-  <si>
     <t>Knight</t>
   </si>
   <si>
@@ -697,13 +694,100 @@
   </si>
   <si>
     <t>Longbowman</t>
+  </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Dark Age</t>
+  </si>
+  <si>
+    <t>No Barracks</t>
+  </si>
+  <si>
+    <t>No Militia</t>
+  </si>
+  <si>
+    <t>Dock only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Fishing Boat only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Transport Ship only on Hard Logic</t>
+  </si>
+  <si>
+    <t>No Loom</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Loom</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>Fishing Trap</t>
+  </si>
+  <si>
+    <t>Fishing Lines</t>
+  </si>
+  <si>
+    <t>Dark - Feudal Age</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Fire Galley</t>
+  </si>
+  <si>
+    <t>Galley</t>
+  </si>
+  <si>
+    <t>Hulk</t>
+  </si>
+  <si>
+    <t>Demolition Raft</t>
+  </si>
+  <si>
+    <t>Trade Cog</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Woad Raider</t>
+  </si>
+  <si>
+    <t>Petard</t>
+  </si>
+  <si>
+    <t>Stronghold</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,23 +822,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
@@ -802,6 +873,30 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -811,7 +906,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -958,11 +1053,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -970,25 +1102,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -997,16 +1129,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1018,59 +1141,101 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1414,58 +1579,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:17" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="45" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1498,11 +1663,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="207" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
+    <row r="5" spans="2:17" ht="188.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="44" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -1518,7 +1683,7 @@
       <c r="H5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="48" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="2"/>
@@ -1532,8 +1697,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="207" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="13" t="s">
+    <row r="6" spans="2:17" ht="169.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="46" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1683,11 +1848,11 @@
       <c r="K10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
       <c r="Q10" s="1" t="s">
         <v>65</v>
       </c>
@@ -1700,15 +1865,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6A4EDC-A2A6-4384-9D45-5513B4018DE4}">
-  <dimension ref="G1:M42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:13" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:13" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -1722,284 +1895,344 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="31" t="s">
+    <row r="3" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="23" t="s">
         <v>94</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="30" t="s">
+    <row r="4" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>79</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="20" t="s">
-        <v>97</v>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-    </row>
-    <row r="8" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-    </row>
-    <row r="9" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="29"/>
-    </row>
-    <row r="14" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="29"/>
-    </row>
-    <row r="15" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="29"/>
-    </row>
-    <row r="16" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="29"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="26"/>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="26"/>
+    </row>
+    <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="26"/>
+    </row>
+    <row r="16" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="29"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="29"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="26"/>
     </row>
     <row r="19" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="29"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="26"/>
     </row>
     <row r="20" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="29"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="29"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="29"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="29"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="29"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="29"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="29"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="29"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
     </row>
     <row r="28" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="29"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="26"/>
     </row>
     <row r="29" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="29"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="29"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="29"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="26"/>
     </row>
     <row r="32" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="29"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="26"/>
     </row>
     <row r="33" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="29"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="26"/>
     </row>
     <row r="34" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="29"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="26"/>
     </row>
     <row r="35" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="29"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="26"/>
     </row>
     <row r="36" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="29"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="26"/>
     </row>
     <row r="37" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="29"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="26"/>
     </row>
     <row r="38" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2007,15 +2240,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE0B8A1-A1CB-49C6-9730-949A4C34C8FA}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2029,340 +2268,412 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="31" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-    </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="31" t="s">
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="19" t="s">
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>75</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-    </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-    </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-    </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="41"/>
+      <c r="C7" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1F63AB-7290-450B-8980-98B8DF63CD4A}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2376,336 +2687,404 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="31" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="28" t="s">
         <v>73</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-    </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="19" t="s">
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>75</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-    </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-    </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-    </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="41"/>
+      <c r="C6" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7768BA2-988B-4725-884E-9A32CD20C2E6}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2719,282 +3098,368 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="31" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-    </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="31" t="s">
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-    </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="19" t="s">
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>75</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="25"/>
       <c r="G6" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="20" t="s">
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="G7" s="17" t="s">
         <v>79</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-    </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="30" t="s">
-        <v>97</v>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="G8" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-    </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-    </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603586A2-08C1-4762-8104-5B2832D5265D}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3008,294 +3473,360 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="31" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="23" t="s">
         <v>94</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="32" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="29" t="s">
         <v>71</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="21" t="s">
-        <v>100</v>
+      <c r="K4" s="18" t="s">
+        <v>99</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="20" t="s">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>79</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="17" t="s">
         <v>70</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="27" t="s">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="25"/>
+      <c r="G6" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="20" t="s">
-        <v>98</v>
+      <c r="L6" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="G7" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-    </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-    </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-    </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-    </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDB17CE-ADDF-47FF-AB15-5D9169E4FB09}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3309,338 +3840,406 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="31" t="s">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="31" t="s">
         <v>72</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="31" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>73</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="17" t="s">
         <v>92</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="19" t="s">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>75</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="17" t="s">
         <v>93</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="41"/>
+      <c r="C6" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="25"/>
       <c r="G6" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="17" t="s">
         <v>78</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="33" t="s">
-        <v>98</v>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="G7" s="30" t="s">
+        <v>97</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="17" t="s">
         <v>89</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="22" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="25"/>
+      <c r="G8" s="19" t="s">
         <v>81</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="17" t="s">
         <v>83</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="21" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="G9" s="18" t="s">
         <v>80</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="17" t="s">
         <v>90</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="20" t="s">
-        <v>97</v>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="G10" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="17" t="s">
         <v>76</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="20" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="25"/>
+      <c r="G11" s="17" t="s">
         <v>77</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="K12" s="20" t="s">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="K12" s="17" t="s">
         <v>84</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="K13" s="27" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="K13" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-    </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
+      <c r="L13" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C3B2F3-07FC-4AA1-B938-54EA265CD689}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3654,164 +4253,214 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G3" s="37" t="s">
-        <v>96</v>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="G3" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="23" t="s">
         <v>92</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="21" t="s">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>101</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="17" t="s">
         <v>93</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G5" s="21" t="s">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>102</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="17" t="s">
         <v>95</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="21" t="s">
-        <v>103</v>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="25"/>
+      <c r="G6" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="17" t="s">
         <v>89</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="21" t="s">
-        <v>86</v>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="25"/>
+      <c r="G7" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="17" t="s">
         <v>83</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G8" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="21" t="s">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="25"/>
+      <c r="K8" s="18" t="s">
         <v>74</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="K9" s="20" t="s">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="K9" s="17" t="s">
         <v>90</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="K10" s="20" t="s">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="K10" s="17" t="s">
         <v>94</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="K11" s="20" t="s">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="K11" s="17" t="s">
         <v>76</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="K12" s="20" t="s">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="K12" s="17" t="s">
         <v>87</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="K13" s="21" t="s">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="K13" s="18" t="s">
         <v>82</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="K14" s="20" t="s">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="K14" s="17" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="K15" s="20" t="s">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="K15" s="17" t="s">
         <v>84</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="K16" s="20" t="s">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="K16" s="17" t="s">
         <v>72</v>
       </c>
       <c r="L16" s="8" t="s">
@@ -3819,9 +4468,9 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="K17" s="20" t="s">
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="K17" s="17" t="s">
         <v>78</v>
       </c>
       <c r="L17" s="8" t="s">
@@ -3829,9 +4478,9 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="K18" s="21" t="s">
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="K18" s="18" t="s">
         <v>91</v>
       </c>
       <c r="L18" s="8" t="s">
@@ -3839,9 +4488,9 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="K19" s="21" t="s">
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="K19" s="18" t="s">
         <v>88</v>
       </c>
       <c r="L19" s="8" t="s">
@@ -3849,144 +4498,148 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="K20" s="35" t="s">
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="K20" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="L20" s="23" t="s">
+      <c r="L20" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago William Wallace.xlsx
+++ b/docs/Logic Requirements/Ageipelago William Wallace.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B3BA43-3F6A-4476-A7F7-5769A803E51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5108BDF-AEF7-40DC-B04B-986497EE0687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" activeTab="7" xr2:uid="{1D996FA3-8E71-4AAB-A721-F834CDA60D66}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="134">
   <si>
     <t>Scenario</t>
   </si>
@@ -781,6 +781,12 @@
   </si>
   <si>
     <t>Stronghold</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Feudal - Imperial Age</t>
   </si>
 </sst>
 </file>
@@ -1196,24 +1202,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1236,6 +1224,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1598,7 +1604,7 @@
       <c r="G3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="41" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="13" t="s">
@@ -1630,7 +1636,7 @@
       </c>
     </row>
     <row r="4" spans="2:17" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1664,10 +1670,10 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="188.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -1683,7 +1689,7 @@
       <c r="H5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="48" t="s">
+      <c r="I5" s="42" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="2"/>
@@ -1698,7 +1704,7 @@
       </c>
     </row>
     <row r="6" spans="2:17" ht="169.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="40" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1877,11 +1883,11 @@
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -1896,11 +1902,11 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -1953,8 +1959,8 @@
       <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="25"/>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
@@ -1962,8 +1968,8 @@
       <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
@@ -1971,8 +1977,8 @@
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -1980,8 +1986,8 @@
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -1989,8 +1995,8 @@
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -1998,8 +2004,8 @@
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -2007,8 +2013,8 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -2016,8 +2022,8 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -2026,8 +2032,8 @@
       <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -2036,8 +2042,8 @@
       <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -2046,8 +2052,8 @@
       <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -2250,11 +2256,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2269,11 +2275,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -2343,7 +2349,7 @@
       <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="28" t="s">
         <v>112</v>
       </c>
@@ -2356,8 +2362,8 @@
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -2367,8 +2373,8 @@
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -2378,8 +2384,8 @@
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -2389,8 +2395,8 @@
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -2400,8 +2406,8 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -2411,8 +2417,8 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -2422,8 +2428,8 @@
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -2433,8 +2439,8 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -2444,8 +2450,8 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -2669,11 +2675,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -2688,11 +2694,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="28" t="s">
         <v>73</v>
       </c>
@@ -2743,7 +2749,7 @@
       <c r="L5" s="25"/>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="41"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="28" t="s">
         <v>112</v>
       </c>
@@ -2756,8 +2762,8 @@
       <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
@@ -2767,8 +2773,8 @@
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -2778,8 +2784,8 @@
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -2789,8 +2795,8 @@
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -2800,8 +2806,8 @@
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -2811,8 +2817,8 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -2822,8 +2828,8 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -2833,8 +2839,8 @@
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -2844,8 +2850,8 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -2855,8 +2861,8 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -3080,11 +3086,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3099,11 +3105,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3152,7 +3158,7 @@
       <c r="L5" s="25"/>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="37" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -3169,7 +3175,7 @@
       <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="37" t="s">
         <v>117</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -3186,7 +3192,7 @@
       <c r="L7" s="25"/>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="37" t="s">
         <v>118</v>
       </c>
       <c r="C8" s="16" t="s">
@@ -3229,7 +3235,7 @@
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="16" t="s">
         <v>127</v>
       </c>
@@ -3240,7 +3246,7 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
+      <c r="B12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -3248,7 +3254,7 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
+      <c r="B13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -3256,8 +3262,8 @@
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -3265,8 +3271,8 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -3274,8 +3280,8 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -3455,11 +3461,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3474,11 +3480,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3539,8 +3545,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="25"/>
       <c r="G6" s="33" t="s">
         <v>98</v>
@@ -3556,8 +3562,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="25"/>
       <c r="G7" s="17" t="s">
         <v>97</v>
@@ -3569,8 +3575,8 @@
       <c r="L7" s="21"/>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -3578,8 +3584,8 @@
       <c r="L8" s="25"/>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -3587,8 +3593,8 @@
       <c r="L9" s="25"/>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -3596,8 +3602,8 @@
       <c r="L10" s="25"/>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -3605,8 +3611,8 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -3614,8 +3620,8 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -3623,8 +3629,8 @@
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -3632,8 +3638,8 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -3641,8 +3647,8 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -3822,11 +3828,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -3841,11 +3847,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3906,7 +3912,7 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="41"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="28" t="s">
         <v>130</v>
       </c>
@@ -3925,8 +3931,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="25"/>
       <c r="G7" s="30" t="s">
         <v>97</v>
@@ -3942,8 +3948,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="25"/>
       <c r="G8" s="19" t="s">
         <v>81</v>
@@ -3959,8 +3965,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="G9" s="18" t="s">
         <v>80</v>
@@ -3976,8 +3982,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="G10" s="17" t="s">
         <v>96</v>
@@ -3993,8 +3999,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="25"/>
       <c r="G11" s="17" t="s">
         <v>77</v>
@@ -4010,8 +4016,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -4023,8 +4029,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -4036,8 +4042,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -4045,8 +4051,8 @@
       <c r="L14" s="21"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -4054,8 +4060,8 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -4235,11 +4241,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
       <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
@@ -4254,11 +4260,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="G3" s="18" t="s">
         <v>100</v>
       </c>
@@ -4319,8 +4325,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="25"/>
       <c r="G6" s="18" t="s">
         <v>86</v>
@@ -4336,8 +4342,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="25"/>
       <c r="G7" s="17" t="s">
         <v>77</v>
@@ -4353,8 +4359,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="25"/>
       <c r="K8" s="18" t="s">
         <v>74</v>
@@ -4364,8 +4370,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -4377,8 +4383,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -4390,8 +4396,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -4403,8 +4409,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -4416,8 +4422,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -4429,8 +4435,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
@@ -4442,8 +4448,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
@@ -4455,8 +4461,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
@@ -4641,5 +4647,6 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>